--- a/spectral_centroid/DS-1W複合音_スペクトル重心.xlsx
+++ b/spectral_centroid/DS-1W複合音_スペクトル重心.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\recording_application\spectral_centroid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F9FE87-2121-4E07-9EA2-1A1C1F7F6A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D3D3C4-750B-47CD-BB4F-6E1C2E5ED543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17256" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -497,61 +497,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>スペクトル重心</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -930,7 +875,6 @@
         <c:axId val="1891396672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="6000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -948,61 +892,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>スペクトル重心</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2583,16 +2472,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2601,7 +2490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2621,7 +2510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -2644,7 +2533,7 @@
         <v>4378</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2667,7 +2556,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -2690,7 +2579,7 @@
         <v>5719</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2698,7 +2587,7 @@
         <v>4056</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -2706,7 +2595,7 @@
         <v>4376</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -2714,7 +2603,7 @@
         <v>4378</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -2722,7 +2611,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2730,7 +2619,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -2738,7 +2627,7 @@
         <v>4155</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -2746,7 +2635,7 @@
         <v>4171</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -2754,7 +2643,7 @@
         <v>4505</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -2762,7 +2651,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
@@ -2770,7 +2659,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
@@ -2778,7 +2667,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
@@ -2786,7 +2675,7 @@
         <v>5288</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
@@ -2794,7 +2683,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -2802,7 +2691,7 @@
         <v>5657</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -2810,7 +2699,7 @@
         <v>5719</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>1</v>
       </c>
